--- a/schemes/физическая модель.xlsx
+++ b/schemes/физическая модель.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VIKUSIK\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAFC9CE2-990A-4CA8-A221-D63FFC729A7C}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6515EC-6BB3-4DEE-BB97-AB77EFAEAB0D}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{D137F1CD-9C73-421A-874F-531DE09EE9FF}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="79">
   <si>
     <t>Название</t>
   </si>
@@ -198,9 +198,6 @@
     <t>NOT NULL CHECK (price &gt;= 0)</t>
   </si>
   <si>
-    <t>NOT NULL REFERENCES supplier(supplier_id) ON DELETE RESTRICT</t>
-  </si>
-  <si>
     <t>NOT NULL DEFAULT 0 CHECK (quantity_on_hand &gt;= 0)</t>
   </si>
   <si>
@@ -243,22 +240,28 @@
     <t>NOT NULL CHECK (status IN ('new','processing','shipped','delivered','cancelled'))</t>
   </si>
   <si>
-    <t>NOT NULL REFERENCES client(client_id) ON DELETE RESTRICT</t>
-  </si>
-  <si>
-    <t>NOT NULL REFERENCES product(product_id) ON DELETE RESTRICT</t>
-  </si>
-  <si>
-    <t>NOT NULL REFERENCES warehouse(warehouse_id) ON DELETE RESTRICT</t>
-  </si>
-  <si>
-    <t>NOT NULL REFERENCES employee(employee_id) ON DELETE RESTRICT</t>
-  </si>
-  <si>
     <t>NOT NULL CHECK (quantity &gt; 0)</t>
   </si>
   <si>
     <t>NOT NULL CHECK (position &lt;&gt; ' ')</t>
+  </si>
+  <si>
+    <t>FK -&gt; SUPPLIER(supplier_id)</t>
+  </si>
+  <si>
+    <t>FK -&gt; CLIENT(client_id)</t>
+  </si>
+  <si>
+    <t>FK -&gt; WAREHOUSE(warehouse_id)</t>
+  </si>
+  <si>
+    <t>FK -&gt; EMPLOYEE(employee_id)</t>
+  </si>
+  <si>
+    <t>FK -&gt; PRODUCT(product_id)</t>
+  </si>
+  <si>
+    <t>VARCHAR(15)</t>
   </si>
 </sst>
 </file>
@@ -336,15 +339,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -674,18 +677,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="G1" s="4" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="G1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -778,7 +781,7 @@
       <c r="D5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>44</v>
       </c>
       <c r="H5" s="2" t="s">
@@ -806,12 +809,12 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
       <c r="G7" s="2" t="s">
         <v>36</v>
       </c>
@@ -821,8 +824,8 @@
       <c r="I7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="5" t="s">
-        <v>57</v>
+      <c r="J7" s="4" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -848,7 +851,7 @@
         <v>54</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -878,15 +881,15 @@
       <c r="D10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
+      <c r="G10" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -919,16 +922,16 @@
         <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>9</v>
@@ -947,43 +950,43 @@
       <c r="C13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G14" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="J13" s="2" t="s">
+      <c r="I14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G14" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
       <c r="G15" s="2" t="s">
         <v>17</v>
       </c>
@@ -994,7 +997,7 @@
         <v>54</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -1019,8 +1022,8 @@
       <c r="I16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="J16" s="5" t="s">
-        <v>74</v>
+      <c r="J16" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -1040,13 +1043,13 @@
         <v>29</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>54</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1057,7 +1060,7 @@
         <v>32</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>13</v>
@@ -1065,18 +1068,18 @@
       <c r="G18" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="5" t="s">
         <v>47</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>54</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -1086,19 +1089,19 @@
         <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="I19" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I19" s="6" t="s">
         <v>54</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1108,12 +1111,12 @@
       <c r="D20" s="1"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
@@ -1158,7 +1161,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B25" s="2" t="s">

--- a/schemes/физическая модель.xlsx
+++ b/schemes/физическая модель.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VIKUSIK\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VIKUSIK\Desktop\ds\database-project\schemes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6515EC-6BB3-4DEE-BB97-AB77EFAEAB0D}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F523644-DC43-44CE-BB95-9C69A628587B}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{D137F1CD-9C73-421A-874F-531DE09EE9FF}"/>
   </bookViews>
@@ -240,28 +240,28 @@
     <t>NOT NULL CHECK (status IN ('new','processing','shipped','delivered','cancelled'))</t>
   </si>
   <si>
-    <t>NOT NULL CHECK (quantity &gt; 0)</t>
-  </si>
-  <si>
     <t>NOT NULL CHECK (position &lt;&gt; ' ')</t>
   </si>
   <si>
-    <t>FK -&gt; SUPPLIER(supplier_id)</t>
-  </si>
-  <si>
-    <t>FK -&gt; CLIENT(client_id)</t>
-  </si>
-  <si>
-    <t>FK -&gt; WAREHOUSE(warehouse_id)</t>
-  </si>
-  <si>
-    <t>FK -&gt; EMPLOYEE(employee_id)</t>
-  </si>
-  <si>
-    <t>FK -&gt; PRODUCT(product_id)</t>
-  </si>
-  <si>
     <t>VARCHAR(15)</t>
+  </si>
+  <si>
+    <t>FK -&gt; SUPPLIER(supplier_id) ON DELETE RESTRICT</t>
+  </si>
+  <si>
+    <t>FK -&gt; CLIENT(client_id) ON DELETE RESTRICT</t>
+  </si>
+  <si>
+    <t>FK -&gt; WAREHOUSE(warehouse_id) ON DELETE RESTRICT</t>
+  </si>
+  <si>
+    <t>FK -&gt; EMPLOYEE(employee_id) ON DELETE RESTRICT</t>
+  </si>
+  <si>
+    <t>FK -&gt; PRODUCT(product_id) ON DELETE RESTRICT</t>
+  </si>
+  <si>
+    <t>NOT NULL CHECK (quantity &gt; 0) ON DELETE RESTRICT</t>
   </si>
 </sst>
 </file>
@@ -922,7 +922,7 @@
         <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>13</v>
@@ -1089,7 +1089,7 @@
         <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>62</v>
@@ -1101,7 +1101,7 @@
         <v>54</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
